--- a/word_gen_system/templates/template_relation.xlsx
+++ b/word_gen_system/templates/template_relation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\资料\AI\AI-Document-GS\word_gen_system\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0F524F-7D1E-4591-AD87-0F30DAB73F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC588A1E-0B15-4C20-B309-DCC72E536555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3132" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="3024" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>template_id</t>
   </si>
@@ -55,55 +55,26 @@
     <t>description</t>
   </si>
   <si>
-    <t>branch_main</t>
-  </si>
-  <si>
-    <t>支行主表</t>
-  </si>
-  <si>
     <t>main</t>
   </si>
   <si>
-    <t>loan_summary</t>
-  </si>
-  <si>
-    <t>贷款汇总表</t>
-  </si>
-  <si>
-    <t>aux</t>
-  </si>
-  <si>
-    <t>one_to_one</t>
-  </si>
-  <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>产品明细表</t>
-  </si>
-  <si>
-    <t>one_to_many</t>
-  </si>
-  <si>
-    <t>支行测试报告</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>template_7.docx</t>
-  </si>
-  <si>
-    <t>branch_name</t>
-  </si>
-  <si>
-    <t>branch_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>法人e抵贷款作业数据要素</t>
+  </si>
+  <si>
+    <t>template_9.xlsx</t>
+  </si>
+  <si>
+    <t>data_element</t>
+  </si>
+  <si>
+    <t>数据要素表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +92,19 @@
     <font>
       <sz val="11"/>
       <color rgb="FF344054"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF7A879A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF172033"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -145,9 +129,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -450,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
@@ -501,97 +487,28 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I2" s="1"/>
       <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
